--- a/www/ig/fhir/tddui/StructureDefinition-tddui-entry-mode-label.xlsx
+++ b/www/ig/fhir/tddui/StructureDefinition-tddui-entry-mode-label.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T14:53:05+00:00</t>
+    <t>2026-03-16T15:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/www/ig/fhir/tddui/StructureDefinition-tddui-entry-mode-label.xlsx
+++ b/www/ig/fhir/tddui/StructureDefinition-tddui-entry-mode-label.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:53:20+00:00</t>
+    <t>2026-07-22T14:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
